--- a/survey_templates/033_site_visit_evaluation_checklist--survey_templates.xlsx
+++ b/survey_templates/033_site_visit_evaluation_checklist--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -896,8 +896,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -959,12 +959,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3.1,_'label':_'all_site_visitors_were_met',_'value':_'all'}</t>
+          <t>all_site_visitors_were_met</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3.1, 'label': 'All site visitors were met', 'value': 'All'}</t>
+          <t>All site visitors were met</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_3.2,_'label':_'some_site_visitors_were_met',_'value':_'some'}</t>
+          <t>some_site_visitors_were_met</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 3.2, 'label': 'Some site visitors were met', 'value': 'Some'}</t>
+          <t>Some site visitors were met</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3.3,_'label':_'no_site_visitors_were_met',_'value':_'none'}</t>
+          <t>no_site_visitors_were_met</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3.3, 'label': 'No site visitors were met', 'value': 'None'}</t>
+          <t>No site visitors were met</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_5.1,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 5.1, 'label': 'Excellent', 'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_5.2,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 5.2, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_5.3,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 5.3, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5.4,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5.4, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_6.1,_'label':_'vehicle',_'value':_'vehicle'}</t>
+          <t>vehicle</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 6.1, 'label': 'Vehicle', 'value': 'Vehicle'}</t>
+          <t>Vehicle</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6.2,_'label':_'accomodation',_'value':_'accomodation'}</t>
+          <t>accomodation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6.2, 'label': 'Accomodation', 'value': 'Accomodation'}</t>
+          <t>Accomodation</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_8.1,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 8.1, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_8.2,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 8.2, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_8.3,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 8.3, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_11.1,_'label':_'excellent',_'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 11.1, 'label': 'Excellent', 'value': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_11.2,_'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 11.2, 'label': 'Good', 'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_11.3,_'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 11.3, 'label': 'Fair', 'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_11.4,_'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 11.4, 'label': 'Poor', 'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
